--- a/tableau_synthese.xlsx
+++ b/tableau_synthese.xlsx
@@ -1260,7 +1260,7 @@
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
-          <t>☑ SISR</t>
+          <t>▣ SISR</t>
         </is>
       </c>
       <c r="H4" s="25" t="inlineStr">

--- a/tableau_synthese.xlsx
+++ b/tableau_synthese.xlsx
@@ -618,7 +618,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -789,6 +789,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1197,7 +1200,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="12.75"/>
   <cols>
     <col width="70.42578125" customWidth="1" style="1" min="1" max="1"/>
-    <col width="10.85546875" customWidth="1" style="1" min="2" max="2"/>
+    <col width="24" customWidth="1" style="1" min="2" max="2"/>
     <col width="18.7109375" customWidth="1" style="1" min="3" max="8"/>
     <col width="11.42578125" customWidth="1" min="9" max="43"/>
     <col width="10.85546875" customWidth="1" style="1" min="44" max="16384"/>
@@ -1399,7 +1402,7 @@
 TP réseau — Cisco Packet Tracer</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="64" t="inlineStr">
         <is>
           <t>01/10/24 au 31/10/24</t>
         </is>
@@ -1426,7 +1429,7 @@
 TP système — Infrastructure scolaire</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="64" t="inlineStr">
         <is>
           <t>01/02/25 au 31/03/25</t>
         </is>
@@ -1457,7 +1460,7 @@
 TP sécurité — Infrastructure scolaire</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="64" t="inlineStr">
         <is>
           <t>01/05/25 au 30/06/25</t>
         </is>
@@ -1488,7 +1491,7 @@
 TP système — Infrastructure scolaire — Activité E6</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="64" t="inlineStr">
         <is>
           <t>01/09/25 au 31/01/26</t>
         </is>
@@ -1523,7 +1526,7 @@
 TP ITSM — Infrastructure scolaire — Activité E6</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="64" t="inlineStr">
         <is>
           <t>01/01/26 au 31/03/26</t>
         </is>
@@ -1623,7 +1626,7 @@
 V2SI — Interventions chez les clients</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="64" t="inlineStr">
         <is>
           <t>01/09/24 au 30/06/26</t>
         </is>
@@ -1659,7 +1662,7 @@
 V2SI — Avant chaque intervention client</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="64" t="inlineStr">
         <is>
           <t>01/09/24 au 30/06/26</t>
         </is>
@@ -1695,7 +1698,7 @@
 V2SI — Déploiements clients</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="64" t="inlineStr">
         <is>
           <t>01/10/24 au 30/06/26</t>
         </is>
@@ -1730,7 +1733,7 @@
 Déploiement Docker, HTTPS Let's Encrypt, 2FA TOTP</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="64" t="inlineStr">
         <is>
           <t>01/11/24 au 31/12/24</t>
         </is>
@@ -1765,7 +1768,7 @@
 DNS récursif avec blocage publicités et trackers, DNS over HTTPS</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="64" t="inlineStr">
         <is>
           <t>01/02/25 au 31/03/25</t>
         </is>
@@ -1800,7 +1803,7 @@
 VPN mesh WireGuard, zéro port ouvert sur internet</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="64" t="inlineStr">
         <is>
           <t>01/04/25 au 31/05/25</t>
         </is>
@@ -1859,7 +1862,7 @@
 Certificats Let's Encrypt via challenge DNS, accès HTTPS unifié</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="64" t="inlineStr">
         <is>
           <t>01/09/25 au 31/10/25</t>
         </is>
@@ -1894,7 +1897,7 @@
 Contrôleur de domaine, GPO, DNS, DHCP, partage de fichiers RAID 1</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="64" t="inlineStr">
         <is>
           <t>01/09/25 au 31/01/26</t>
         </is>
@@ -1929,7 +1932,7 @@
 Backrest/Restic local + synchronisation Backblaze B2 via Rclone</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="64" t="inlineStr">
         <is>
           <t>01/11/25 au 31/12/25</t>
         </is>
@@ -1964,7 +1967,7 @@
 UFW, Fail2ban, SSH par clés, mises à jour automatiques</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="64" t="inlineStr">
         <is>
           <t>01/01/26 au 28/02/26</t>
         </is>
@@ -1999,7 +2002,7 @@
 Inventaire du parc, helpdesk, gestion des tickets, intégration LDAP/AD</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="64" t="inlineStr">
         <is>
           <t>01/01/26 au 31/03/26</t>
         </is>
